--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ui_Robot1\Documents\UiPath\Project Cost Data (Dev)\Process 1 - Update Project List\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5592D792-B48D-4507-AAE9-C0F459D40F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5A174A-6FC0-4378-8222-29D0F5868AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,12 +499,6 @@
     <t>strSubjectBusinessErrorReport</t>
   </si>
   <si>
-    <t>Non Production</t>
-  </si>
-  <si>
-    <t>Non Production/Cost Data Automation</t>
-  </si>
-  <si>
     <t>STR_SQL_DATABASENAME</t>
   </si>
   <si>
@@ -675,6 +669,12 @@
   </si>
   <si>
     <t>{MyDocs}\UiPathDocs\Temps_Email</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Production/Cost Data Automation</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -1242,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -1255,42 +1255,42 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C10" s="12"/>
     </row>
@@ -2581,7 +2581,7 @@
         <v>91</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C29" s="12"/>
     </row>
@@ -2590,7 +2590,7 @@
         <v>92</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C30" s="12"/>
     </row>
@@ -2599,7 +2599,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" s="12"/>
     </row>
@@ -2608,7 +2608,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C32" s="12"/>
     </row>
@@ -2617,7 +2617,7 @@
         <v>95</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C33" s="12"/>
     </row>
@@ -2626,7 +2626,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C34" s="12"/>
     </row>
@@ -2635,7 +2635,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C35" s="12"/>
     </row>
@@ -2644,7 +2644,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C36" s="12"/>
     </row>
@@ -2653,7 +2653,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C37" s="12"/>
     </row>
@@ -2857,7 +2857,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C63" s="12"/>
     </row>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="67" spans="1:3" ht="30">
       <c r="A67" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C67" s="12"/>
     </row>
@@ -2902,7 +2902,7 @@
         <v>132</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C68" s="12"/>
     </row>
@@ -2920,55 +2920,55 @@
         <v>135</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C70" s="12"/>
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1">
       <c r="A71" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C71" s="12"/>
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1">
       <c r="A72" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C72" s="12"/>
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1">
       <c r="A73" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C73" s="12"/>
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1">
       <c r="A74" s="12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C74" s="12"/>
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1">
       <c r="A75" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" t="s">
         <v>185</v>
-      </c>
-      <c r="B75" t="s">
-        <v>186</v>
-      </c>
-      <c r="C75" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="14.25" customHeight="1">
@@ -3933,7 +3933,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -3944,7 +3944,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
@@ -3955,7 +3955,7 @@
         <v>30</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -3966,7 +3966,7 @@
         <v>31</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
@@ -3977,7 +3977,7 @@
         <v>32</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
@@ -3988,7 +3988,7 @@
         <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -3999,7 +3999,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D8" s="7">
         <v>14</v>
@@ -4013,7 +4013,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D9" s="7">
         <v>35</v>
@@ -4027,7 +4027,7 @@
         <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>41</v>
@@ -4041,7 +4041,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>41</v>
@@ -4055,7 +4055,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>41</v>
@@ -4069,7 +4069,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>41</v>
@@ -4083,7 +4083,7 @@
         <v>141</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -4094,84 +4094,84 @@
         <v>140</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
